--- a/data/trans_orig/P2A_ner_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15179</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>10812</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22098</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>458597</t>
+          <t>459203</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>469855</t>
+          <t>470056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295980</t>
+          <t>295868</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304808</t>
+          <t>304814</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758359</t>
+          <t>759393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773024</t>
+          <t>773108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21437</t>
+          <t>21308</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>36569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346498</t>
+          <t>346096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360688</t>
+          <t>360341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350428</t>
+          <t>350557</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364763</t>
+          <t>365038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703090</t>
+          <t>702230</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722659</t>
+          <t>722202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25512</t>
+          <t>25170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16223</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36189</t>
+          <t>36382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516877</t>
+          <t>517219</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533352</t>
+          <t>532561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149382</t>
+          <t>150060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163602</t>
+          <t>163603</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>673982</t>
+          <t>673789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>693392</t>
+          <t>693948</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27557</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53221</t>
+          <t>52313</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21751</t>
+          <t>21537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>45224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53809</t>
+          <t>55030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88660</t>
+          <t>88708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1185113</t>
+          <t>1186021</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1210777</t>
+          <t>1210383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669564</t>
+          <t>669061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>692534</t>
+          <t>692748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1863960</t>
+          <t>1863912</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1898811</t>
+          <t>1897590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>19290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41771</t>
+          <t>42052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29201</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53804</t>
+          <t>56082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>331337</t>
+          <t>331265</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344671</t>
+          <t>344951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>526981</t>
+          <t>526700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>548813</t>
+          <t>547898</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>865503</t>
+          <t>863225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890106</t>
+          <t>889775</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51989</t>
+          <t>51197</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83675</t>
+          <t>83077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57657</t>
+          <t>57293</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92405</t>
+          <t>90234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287703</t>
+          <t>288065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296305</t>
+          <t>296333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1165085</t>
+          <t>1165683</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1196771</t>
+          <t>1197563</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1454555</t>
+          <t>1456726</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1489303</t>
+          <t>1489667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73327</t>
+          <t>73512</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>110840</t>
+          <t>110054</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>131451</t>
+          <t>131728</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>178691</t>
+          <t>180654</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218364</t>
+          <t>216517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>279809</t>
+          <t>277614</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3159350</t>
+          <t>3160136</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3196863</t>
+          <t>3196678</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3199433</t>
+          <t>3197470</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3246673</t>
+          <t>3246396</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6368505</t>
+          <t>6370700</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6429950</t>
+          <t>6431797</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17039</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36927</t>
+          <t>34856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411248</t>
+          <t>411962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428444</t>
+          <t>428421</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297415</t>
+          <t>297924</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310455</t>
+          <t>310540</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>714738</t>
+          <t>716809</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>736870</t>
+          <t>737099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28638</t>
+          <t>28921</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25829</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22119</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46692</t>
+          <t>46247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390159</t>
+          <t>389876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408517</t>
+          <t>408650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>312182</t>
+          <t>313058</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329134</t>
+          <t>329399</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710116</t>
+          <t>710561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>734689</t>
+          <t>734600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29874</t>
+          <t>32908</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>18846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21274</t>
+          <t>20911</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41815</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>599541</t>
+          <t>596507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>616292</t>
+          <t>615600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241084</t>
+          <t>241283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254930</t>
+          <t>254976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>847729</t>
+          <t>846252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>868270</t>
+          <t>868633</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39032</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26222</t>
+          <t>25533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>48842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48042</t>
+          <t>47819</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82638</t>
+          <t>81307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1119977</t>
+          <t>1120027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1141207</t>
+          <t>1141735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>714635</t>
+          <t>717815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>740435</t>
+          <t>741124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1843029</t>
+          <t>1844360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1877625</t>
+          <t>1877848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27863</t>
+          <t>27895</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>36284</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62390</t>
+          <t>64135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51309</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85427</t>
+          <t>84046</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>482733</t>
+          <t>482701</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>500829</t>
+          <t>499838</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>699132</t>
+          <t>697387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>726476</t>
+          <t>725238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1186691</t>
+          <t>1188072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1220809</t>
+          <t>1220767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42803</t>
+          <t>41982</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72853</t>
+          <t>71522</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44524</t>
+          <t>45927</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77634</t>
+          <t>75003</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256372</t>
+          <t>256338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265038</t>
+          <t>265029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1036498</t>
+          <t>1037829</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1066548</t>
+          <t>1067369</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1298599</t>
+          <t>1301230</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1331709</t>
+          <t>1330306</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83081</t>
+          <t>83815</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123433</t>
+          <t>124211</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147891</t>
+          <t>148511</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>201311</t>
+          <t>202093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>245531</t>
+          <t>246407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>311322</t>
+          <t>312330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3298477</t>
+          <t>3297699</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3338829</t>
+          <t>3338095</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3348814</t>
+          <t>3348032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3402234</t>
+          <t>3401614</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6660713</t>
+          <t>6659705</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6726504</t>
+          <t>6725628</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>23978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47346</t>
+          <t>48070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406917</t>
+          <t>406656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422483</t>
+          <t>422004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>313539</t>
+          <t>314225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>333310</t>
+          <t>333479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>728801</t>
+          <t>728077</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>753182</t>
+          <t>752169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42666</t>
+          <t>41365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>355879</t>
+          <t>354817</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>370012</t>
+          <t>370051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345303</t>
+          <t>345204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362494</t>
+          <t>362709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>706834</t>
+          <t>708135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>728697</t>
+          <t>729340</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42331</t>
+          <t>41200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34916</t>
+          <t>35191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39647</t>
+          <t>41056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68150</t>
+          <t>71051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479583</t>
+          <t>480714</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501448</t>
+          <t>501851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131207</t>
+          <t>130932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150184</t>
+          <t>150454</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619886</t>
+          <t>616985</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>648389</t>
+          <t>646980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39609</t>
+          <t>40736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69160</t>
+          <t>69579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59854</t>
+          <t>59205</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93764</t>
+          <t>93590</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108382</t>
+          <t>107837</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151068</t>
+          <t>151960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1080478</t>
+          <t>1080059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1110029</t>
+          <t>1108902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>732112</t>
+          <t>732286</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>766022</t>
+          <t>766671</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1824446</t>
+          <t>1823554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1867132</t>
+          <t>1867677</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23585</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>44683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102816</t>
+          <t>100682</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144292</t>
+          <t>141191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130849</t>
+          <t>131787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>180007</t>
+          <t>182269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>575234</t>
+          <t>576023</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>597121</t>
+          <t>597757</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>593952</t>
+          <t>597053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>635428</t>
+          <t>637562</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1178943</t>
+          <t>1176681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1228101</t>
+          <t>1227163</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110032</t>
+          <t>111653</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>155947</t>
+          <t>155671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121715</t>
+          <t>121066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169101</t>
+          <t>168902</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270215</t>
+          <t>269315</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282272</t>
+          <t>282235</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>926078</t>
+          <t>926354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>971993</t>
+          <t>970372</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1200069</t>
+          <t>1200268</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1247455</t>
+          <t>1248104</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131101</t>
+          <t>131565</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179647</t>
+          <t>178462</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>350571</t>
+          <t>350254</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>427854</t>
+          <t>430591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>497514</t>
+          <t>503363</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>590193</t>
+          <t>591015</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3206075</t>
+          <t>3207260</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3254621</t>
+          <t>3254157</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3103742</t>
+          <t>3101005</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3181025</t>
+          <t>3181342</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6327125</t>
+          <t>6326303</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6419804</t>
+          <t>6413955</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>27775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>18842</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40314</t>
+          <t>39186</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>476597</t>
+          <t>477437</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494293</t>
+          <t>494557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>432287</t>
+          <t>431908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>441970</t>
+          <t>441648</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>912365</t>
+          <t>913493</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>933110</t>
+          <t>933837</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>26144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19614</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40399</t>
+          <t>39262</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>432608</t>
+          <t>431256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447157</t>
+          <t>446460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356301</t>
+          <t>356436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371808</t>
+          <t>371308</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>794394</t>
+          <t>795531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>815179</t>
+          <t>815010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28192</t>
+          <t>29715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12485</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37607</t>
+          <t>36881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640072</t>
+          <t>638549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663643</t>
+          <t>663907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154426</t>
+          <t>154220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162428</t>
+          <t>162412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>797568</t>
+          <t>798294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>825718</t>
+          <t>826607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22938</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44621</t>
+          <t>43579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35358</t>
+          <t>36122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>584428</t>
+          <t>528542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65870</t>
+          <t>67146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>773350</t>
+          <t>845847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>990198</t>
+          <t>991240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1011881</t>
+          <t>1012168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>393666</t>
+          <t>449552</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>942736</t>
+          <t>941972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1239562</t>
+          <t>1167065</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1947042</t>
+          <t>1945766</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>14618</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34185</t>
+          <t>33888</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31862</t>
+          <t>32118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57215</t>
+          <t>58551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52021</t>
+          <t>52104</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82262</t>
+          <t>84021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>440861</t>
+          <t>441158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>459682</t>
+          <t>460428</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>784120</t>
+          <t>782784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>809473</t>
+          <t>809217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1234119</t>
+          <t>1232360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1264360</t>
+          <t>1264277</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>30776</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52133</t>
+          <t>53163</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35152</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60170</t>
+          <t>60101</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226755</t>
+          <t>227885</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239629</t>
+          <t>239645</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>709238</t>
+          <t>708208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>730032</t>
+          <t>730595</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>941708</t>
+          <t>941777</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>966726</t>
+          <t>967216</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74365</t>
+          <t>77453</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126262</t>
+          <t>124947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152346</t>
+          <t>153023</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>963300</t>
+          <t>977834</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>251185</t>
+          <t>250022</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1096573</t>
+          <t>1143922</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3249798</t>
+          <t>3251113</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3301695</t>
+          <t>3298607</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2614458</t>
+          <t>2599924</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3425412</t>
+          <t>3424735</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5857245</t>
+          <t>5809896</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6702633</t>
+          <t>6703796</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_ner_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>14574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21064</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>459203</t>
+          <t>459202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470056</t>
+          <t>469945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295868</t>
+          <t>295759</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304814</t>
+          <t>304836</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>759393</t>
+          <t>758882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773108</t>
+          <t>773129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20838</t>
+          <t>21266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>20554</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36569</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346096</t>
+          <t>345668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360341</t>
+          <t>360065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350557</t>
+          <t>351311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365038</t>
+          <t>364849</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702230</t>
+          <t>702633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722202</t>
+          <t>722237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25170</t>
+          <t>25129</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16223</t>
+          <t>16736</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36382</t>
+          <t>37255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517219</t>
+          <t>517260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>532561</t>
+          <t>533137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150060</t>
+          <t>149682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163603</t>
+          <t>163658</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>673789</t>
+          <t>672916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>693948</t>
+          <t>693435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27951</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52313</t>
+          <t>53248</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21537</t>
+          <t>21503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45224</t>
+          <t>42066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55030</t>
+          <t>54553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88708</t>
+          <t>90614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1186021</t>
+          <t>1185086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1210383</t>
+          <t>1211468</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669061</t>
+          <t>672219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>692748</t>
+          <t>692782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1863912</t>
+          <t>1862006</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897590</t>
+          <t>1898067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19290</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42052</t>
+          <t>42862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56082</t>
+          <t>56352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>331265</t>
+          <t>330475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344951</t>
+          <t>344630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>526700</t>
+          <t>525890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>547898</t>
+          <t>548607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>863225</t>
+          <t>862955</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>889775</t>
+          <t>890143</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51197</t>
+          <t>52299</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83077</t>
+          <t>83513</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57293</t>
+          <t>56163</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90234</t>
+          <t>91155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288065</t>
+          <t>286729</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296333</t>
+          <t>296383</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1165683</t>
+          <t>1165247</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1197563</t>
+          <t>1196461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1456726</t>
+          <t>1455805</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1489667</t>
+          <t>1490797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73512</t>
+          <t>74296</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>110054</t>
+          <t>111671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>131728</t>
+          <t>134048</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>180654</t>
+          <t>182198</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216517</t>
+          <t>215436</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>277614</t>
+          <t>276628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3160136</t>
+          <t>3158519</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3196678</t>
+          <t>3195894</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3197470</t>
+          <t>3195926</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3246396</t>
+          <t>3244076</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6370700</t>
+          <t>6371686</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6431797</t>
+          <t>6432878</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>27454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>36879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411962</t>
+          <t>409757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428421</t>
+          <t>428476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297924</t>
+          <t>298196</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310540</t>
+          <t>310782</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>716809</t>
+          <t>714786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>737099</t>
+          <t>736176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28921</t>
+          <t>27941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24953</t>
+          <t>25221</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46247</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389876</t>
+          <t>390856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408650</t>
+          <t>408550</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313058</t>
+          <t>312790</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329399</t>
+          <t>329410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710561</t>
+          <t>711020</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>734600</t>
+          <t>735601</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13815</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32908</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>17471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20911</t>
+          <t>21031</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>42454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>596507</t>
+          <t>599206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>615600</t>
+          <t>616283</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241283</t>
+          <t>242658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254976</t>
+          <t>255138</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>846252</t>
+          <t>847090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>868633</t>
+          <t>868513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>17708</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>40280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25533</t>
+          <t>25134</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48842</t>
+          <t>49072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47819</t>
+          <t>48968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81307</t>
+          <t>81562</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1120027</t>
+          <t>1118729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1141735</t>
+          <t>1141301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>717815</t>
+          <t>717585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>741124</t>
+          <t>741523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1844360</t>
+          <t>1844105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1877848</t>
+          <t>1876699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27895</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36284</t>
+          <t>36275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64135</t>
+          <t>62146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51351</t>
+          <t>51379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84046</t>
+          <t>84312</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>482701</t>
+          <t>483221</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>499838</t>
+          <t>499704</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>697387</t>
+          <t>699376</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>725238</t>
+          <t>725247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1188072</t>
+          <t>1187806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1220767</t>
+          <t>1220739</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41982</t>
+          <t>41555</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71522</t>
+          <t>72174</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>46847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75003</t>
+          <t>77679</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256338</t>
+          <t>256459</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265029</t>
+          <t>265024</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1037829</t>
+          <t>1037177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1067369</t>
+          <t>1067796</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1301230</t>
+          <t>1298554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1330306</t>
+          <t>1329386</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83815</t>
+          <t>84116</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124211</t>
+          <t>125128</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148511</t>
+          <t>150629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>202093</t>
+          <t>202903</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>246407</t>
+          <t>245424</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>312330</t>
+          <t>311181</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3297699</t>
+          <t>3296782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3338095</t>
+          <t>3337794</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3348032</t>
+          <t>3347222</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3401614</t>
+          <t>3399496</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6659705</t>
+          <t>6660854</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6725628</t>
+          <t>6726611</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22436</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>13242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32830</t>
+          <t>32185</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>23054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48070</t>
+          <t>47620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406656</t>
+          <t>406911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422004</t>
+          <t>422152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>314225</t>
+          <t>314870</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>333479</t>
+          <t>333813</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>728077</t>
+          <t>728527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>752169</t>
+          <t>753093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>22438</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>24763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41365</t>
+          <t>42705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354817</t>
+          <t>354789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>370051</t>
+          <t>369463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345204</t>
+          <t>347510</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362709</t>
+          <t>364045</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708135</t>
+          <t>706795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>729340</t>
+          <t>730168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>20117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41200</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35191</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41056</t>
+          <t>39936</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71051</t>
+          <t>68660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>480714</t>
+          <t>479851</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501851</t>
+          <t>501797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130932</t>
+          <t>130416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150454</t>
+          <t>151062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616985</t>
+          <t>619376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>646980</t>
+          <t>648100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40736</t>
+          <t>40791</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69579</t>
+          <t>71488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59205</t>
+          <t>59556</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93590</t>
+          <t>91950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107837</t>
+          <t>107241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151960</t>
+          <t>152395</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1080059</t>
+          <t>1078150</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1108902</t>
+          <t>1108847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>732286</t>
+          <t>733926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>766671</t>
+          <t>766320</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1823554</t>
+          <t>1823119</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1867677</t>
+          <t>1868273</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>23970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44683</t>
+          <t>45991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100682</t>
+          <t>101856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>141191</t>
+          <t>141212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131787</t>
+          <t>132483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>182269</t>
+          <t>177560</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>576023</t>
+          <t>574715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>597757</t>
+          <t>596736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>597053</t>
+          <t>597032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>637562</t>
+          <t>636388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1176681</t>
+          <t>1181390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1227163</t>
+          <t>1226467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111653</t>
+          <t>111980</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>155671</t>
+          <t>154700</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121066</t>
+          <t>120751</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>168902</t>
+          <t>167636</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269315</t>
+          <t>269020</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282235</t>
+          <t>281984</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>926354</t>
+          <t>927325</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>970372</t>
+          <t>970045</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1200268</t>
+          <t>1201534</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1248104</t>
+          <t>1248419</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131565</t>
+          <t>130015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178462</t>
+          <t>179602</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>350254</t>
+          <t>351601</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>430591</t>
+          <t>428009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>503363</t>
+          <t>495034</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>591015</t>
+          <t>590774</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3207260</t>
+          <t>3206120</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3254157</t>
+          <t>3255707</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3101005</t>
+          <t>3103587</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3181342</t>
+          <t>3179995</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6326303</t>
+          <t>6326544</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6413955</t>
+          <t>6422284</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>19881</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>11840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27775</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>17648</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27545</t>
+          <t>30610</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39186</t>
+          <t>43637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>487263</t>
+          <t>530737</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>477437</t>
+          <t>519988</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494557</t>
+          <t>538778</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>437870</t>
+          <t>477682</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>431908</t>
+          <t>470763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>441648</t>
+          <t>481792</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>925134</t>
+          <t>1008419</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>913493</t>
+          <t>995392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>933837</t>
+          <t>1017204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>23352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>19045</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>28323</t>
+          <t>30969</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39262</t>
+          <t>44697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>441149</t>
+          <t>471288</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>431256</t>
+          <t>459860</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446460</t>
+          <t>477340</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>365321</t>
+          <t>404098</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356436</t>
+          <t>395009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371308</t>
+          <t>410948</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>806470</t>
+          <t>875386</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>795531</t>
+          <t>861658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>815010</t>
+          <t>884262</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29715</t>
+          <t>30271</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36881</t>
+          <t>40581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>652645</t>
+          <t>452155</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638549</t>
+          <t>441341</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663907</t>
+          <t>460189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159190</t>
+          <t>178119</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154220</t>
+          <t>171348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162412</t>
+          <t>182032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>811835</t>
+          <t>630274</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>798294</t>
+          <t>618528</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>826607</t>
+          <t>638780</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32045</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43579</t>
+          <t>46638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>236496</t>
+          <t>37221</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36122</t>
+          <t>28467</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>528542</t>
+          <t>47674</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>268541</t>
+          <t>71463</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67146</t>
+          <t>56876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>845847</t>
+          <t>87755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1002774</t>
+          <t>1097601</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>991240</t>
+          <t>1085205</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1012168</t>
+          <t>1107838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>741598</t>
+          <t>823990</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449552</t>
+          <t>813537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>941972</t>
+          <t>832744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1744371</t>
+          <t>1921591</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1167065</t>
+          <t>1905299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1945766</t>
+          <t>1936178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23185</t>
+          <t>24351</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33888</t>
+          <t>35467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>50937</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32118</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58551</t>
+          <t>62887</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>67877</t>
+          <t>75288</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52104</t>
+          <t>59080</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>90696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>451861</t>
+          <t>543613</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>441158</t>
+          <t>532497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>460428</t>
+          <t>552250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>796643</t>
+          <t>779913</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>782784</t>
+          <t>767963</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>809217</t>
+          <t>790226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1248504</t>
+          <t>1323526</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1232360</t>
+          <t>1308118</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1264277</t>
+          <t>1339734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12622</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40815</t>
+          <t>43496</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30776</t>
+          <t>32785</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53163</t>
+          <t>56085</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>46921</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34662</t>
+          <t>34943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60101</t>
+          <t>59831</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236347</t>
+          <t>233802</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227885</t>
+          <t>226475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239645</t>
+          <t>236397</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>720556</t>
+          <t>800785</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>708208</t>
+          <t>788196</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>730595</t>
+          <t>811496</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>956903</t>
+          <t>1034588</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>941777</t>
+          <t>1021678</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>967216</t>
+          <t>1046566</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>104022</t>
+          <t>113281</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77453</t>
+          <t>93733</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124947</t>
+          <t>136962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>356581</t>
+          <t>170806</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>153023</t>
+          <t>150156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>977834</t>
+          <t>197664</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>460602</t>
+          <t>284086</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250022</t>
+          <t>253127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1143922</t>
+          <t>316646</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3272038</t>
+          <t>3329195</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3251113</t>
+          <t>3305514</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3298607</t>
+          <t>3348743</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3221177</t>
+          <t>3464587</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2599924</t>
+          <t>3437729</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3424735</t>
+          <t>3485237</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6493216</t>
+          <t>6793783</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5809896</t>
+          <t>6761223</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6703796</t>
+          <t>6824742</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_ner_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
